--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -3,29 +3,30 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="9" activeTab="11" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="분석목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_거래처 전기_당기 비교" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_벤포드 분석" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="08_상대계정 분석" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="10_라운드넘버 분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="11_특수관계자 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="13_매출 vs 비용 교차" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="14_심층분석 (계정별 Top) " sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="17_거래처분석" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="21_총계정원장" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="22_은행조회서 완전성" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="23_계정별 상세거래내역" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="24_리스완전성" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="25_손익월별분析" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="26_AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="27_감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="유형자산_처분손익" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="02_거래처 전기_당기 비교" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="03_벤포드 분석" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="08_상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="10_라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="17_거래처분석" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="21_총계정원장" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="22_은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="23_계정별 상세거래내역" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="24_리스완전성" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="25_손익월별분析" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="26_AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="27_감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="유형자산_처분손익" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -37,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -104,6 +105,13 @@
       <i val="1"/>
       <color rgb="FF375623"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="9">
@@ -203,7 +211,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -264,6 +272,10 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -719,6 +731,100 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>단기금융상품_MMF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>단기금융상품_정기예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>미지급금(거래처)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>미지급금(사원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>미지급비용(급여)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>미지급비용(신용카드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>미지급비용(이자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>외주가공비(제조)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -904,7 +1010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1149,7 +1255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1838,13 +1944,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="20.25" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
@@ -1920,19 +2026,12 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>fzj</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2630,7 +2729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2708,7 +2807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
@@ -2894,7 +2993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2935,7 +3034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3093,7 +3192,721 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="20" min="1" max="1"/>
+    <col width="26" customWidth="1" style="20" min="2" max="2"/>
+    <col width="42" customWidth="1" style="20" min="3" max="3"/>
+    <col width="60" customWidth="1" style="20" min="4" max="4"/>
+    <col width="34" customWidth="1" style="20" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>분석번호</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>파라미터 시트명</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>필요 컬럼</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>작성방법</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(공통)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>분석목록 시트의 '분석명'은 아래 파라미터 시트명과 철자가 정확히 같아야 연결됩니다 (예: 분석명 '벤포드 분석' ↔ 시트명 '벤포드 분석'). 파라미터 시트 내 '실행여부' 열이 있는 경우 그 열이 Y(또는 O)인 행만 처리되고, 없는 시트는 적힌 행 전부가 처리됩니다.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>분석목록 자체의 실행여부는 메뉴 On/Off, 파라미터 시트의 실행여부는 그 메뉴 내 항목별 On/Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>거래처 전기_당기 비교</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>계정과목 / 금액열(차변·대변·both) / 실행여부 / 비고 / 관리단위(선택) / 비용구분(선택)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>계정과목 한 줄에 하나씩. 지정한 방향(차변/대변)의 거래처별 전기·당기 금액을 비교표로 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>벤포드 분석</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>계정과목 / 금액열 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>벤포드 법칙을 적용할 계정·방향 지정. 데이터 5건 미만이면 자동으로 "데이터 부족" 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(파라미터 시트 없음)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>분석목록에서 실행여부만 Y로 두면 전체 데이터 요약이 자동 생성됨</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>파라미터 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(파라미터 시트 없음)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>분석목록에서 실행여부만 Y로 두면 계정명 목록·통계가 자동 생성됨</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>파라미터 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(파라미터 시트 없음)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>사원명 컬럼을 자동 탐지해 집계 (컬럼명이 "사원명"이 아니면 preprocess.py에서 먼저 매핑 필요)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>파라미터 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>일자차이 분석 (시트 미생성)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>기준일수 / 실행여부</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>쓰려면 시트명을 정확히 '일자차이 분석'으로 새로 만들고 기준일수(예: 30) 입력. 전표일자 대비 등록일자가 그 일수 이상 지연된 전표를 추출</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>등록일자 계열 컬럼이 있어야 동작</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>상대계정 분석</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>계정과목 / 금액열 / 그룹기준열 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>그룹기준열은 비워두면 전표그룹키(같은 전표를 묶는 내부 키)를 자동 사용 — 보통 비워두는 게 안전</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>키워드검색 (시트 미생성)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>키워드 / 실행여부</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>쓰려면 시트명을 정확히 '키워드검색'으로 새로 만들고 키워드를 한 줄씩 입력 (적요 컬럼에서 검색)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>라운드넘버 분석</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>계정과목 / 금액열 / 최소금액 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>계정과목에 '(전체)' 입력 시 전 계정 대상. 최소금액 이상 배수(10만/50만/100만/500만/1000만원)만 라운드로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>특수관계자 분석</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>거래처명 / 실행여부</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>거래처명은 부분일치 검색 (예: "판타지오" 입력 시 "(주)판타지오"도 매칭)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>자산 vs 부채 교차 (시트 미생성)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>구분(자산/부채) / 계정과목</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>쓰려면 시트명을 정확히 '자산 vs 부채 교차'로 새로 만들고, 구분별 계정과목을 한 줄씩 입력</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>같은 거래처에서 자산·부채 계정이 동시에 발생하는 경우 추출</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>매출 vs 비용 교차</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>구분(매출/비용) / 계정과목 / 비용구분(선택)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>구분별로 계정과목을 한 줄씩 입력. 같은 거래처에서 매출·비용이 동시에 발생하는 경우를 찾음</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심층분석 (계정별 Top) </t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>계정과목 (선택: 개수 / 금액열 열 추가 가능)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>계정과목만 한 줄씩 나열해도 동작 (기본값: 상위 10건, 차대변 모두). 열을 추가하면 개수·방향 지정 가능</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>열 이름은 정확히 '개수', '금액열'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AI계정별분석 (시트 미생성)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>계정과목 / 실행여부</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>쓰려면 시트명을 정확히 'AI계정별분석'으로 새로 만들고 계정과목 입력. Gemini 호출 없이 월별추이·샘플만 추출(26번과 형식은 같으나 AI 분석은 안 함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>(파라미터 시트 없음)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>컬럼 인식 현황(O/X) 점검용. 실데이터 넣고 가장 먼저 돌려보면 좋음</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>파라미터 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>거래처분석</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>작업명 / 계정과목 / 거래처명 / 금액열 / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>작업명은 자유 기재. 계정과목·거래처명은 콤마로 여러 개 지정 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>벤포드이탈 (시트 미생성)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>계정과목 / 금액열 / 임계값 / 최대건수 / 실행여부</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>쓰려면 시트명을 정확히 '벤포드이탈'로 새로 만들 것. 벤포드 법칙에서 크게 벗어난 전표를 상세 추출</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(파라미터 시트 없음)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>전 계정 월별 차변/대변 집계가 자동 생성됨</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>파라미터 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>잔액증감분석 (게정별 거래처벌)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>계정명 / 구분(차변·대변 또는 자산·부채)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>data/previous 폴더에 전기 "계정별_거래처별명세" 파일이 있어야 기초잔액이 채워짐 (없으면 오류 시트만 생성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>총계정원장</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>구분 / 계정과목</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>구분은 시트명 접두어로만 쓰이는 자유 기재 항목(예: 자산/부채). data에 연도가 2개 이상 섞여 있으면 연도비교 표로 자동 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>은행조회서 완전성</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>비워두면 기본 계정(이자비용/단기차입금/장기차입금/전환사채 등)을 자동 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>계정별 상세거래내역</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>계정과목 / 금액유형(차변·대변·차변대변모두) / 실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>리스완전성</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>계정과목 / 실행여부</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>비워두면 기본 계정(임차료/지급수수료/차량유지비/건물관리비/렌탈)을 자동 사용</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>결과는 별도 파일로 저장됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>손익월별분석</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>계정과목 / 구분(차변·대변·both) / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AI계정별분석_실행</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>계정과목 / 실행여부</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 비용 발생)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>감가상각_평가손익분석</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>계정과목 / 금액열 / 그룹기준열 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>★계정과목에는 유형자산명이 아니라 '손익 계정명'을 적음 (예: 감가상각비, 외화환산손익, 평가손익, 대손상각비). 8번 상대계정분석과 완전히 동일한 로직(Phase 1)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>유형자산 롤포워드/처분손익은 아래 두 시트로 별도 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>27-Phase2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>감가상각_유형자산롤포워드</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>유형자산계정명 / 감가상각누계액계정명 / 대체상대계정 / 취득원가_수동조정 / 상각누계액_수동조정 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>27번이 실행여부 Y이고 이 시트에서 실행여부 Y인 행이 있으면 자동 실행됨 (분석목록에 별도 번호 없음). 대체상대계정은 계정대체가 있을 때만 입력(콤마로 여러 개 가능), 없으면 비워둠. 수동조정 2종은 전표매칭으로 못 잡는 잔여차이를 감사인이 직접 숫자로 입력(기본 0)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>비워두면(실행여부 Y행 0개) 조용히 건너뛰고 27번은 Phase1만 결과로 나옴 — 에러 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>27-Phase3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>유형자산_처분손익</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>처분이익계정명 / 처분손실계정명 / 실행여부 / 비고</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>27번 + 위 롤포워드 시트가 모두 있어야 자동 실행됨. 처분이익·처분손실 계정이 등장한 전표마다 같은 전표의 유형자산 취득원가·감가상각누계액을 찾아 처분 건별로 한 줄씩 명세 생성</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>개별 자산이 아닌 계정과목×전표 단위로만 구분됨 — 한 전표에 여러 자산을 묶어 처분하면 한 줄로 잡힘</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>공통-선택</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>관리단위 / 비용구분 열 (2·13·17·25번 시트)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>관리단위(Y) / 비용구분(Y) — 선택 열</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>원장에 '비용구분'(판관/제조 등) 컬럼이 있는 회사 전용 옵션. 계정 행에 Y(또는 O)를 적으면 그 계정의 결과를 비용구분 값별로 나눠서 추출함 (예: 급여 → 급여(판관)·급여(제조)). 관리단위 열도 같은 방식으로 원장의 '전표관리단위'(본사/2공장 등) 컬럼 기준으로 나눔 (13번 시트는 비용구분만 지원).</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>비워두거나 원장에 해당 컬럼이 없으면 무시되고 기존과 동일하게 계정 단위로만 집계됨 — 에러 아님. 열이 없는 task_list는 헤더에 직접 추가해서 사용</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3397,7 +4210,63 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="16.25" bestFit="1" customWidth="1" style="20" min="1" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>처분이익계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>처분손실계정명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>유형자산처분이익</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>유형자산처분손실</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4023,7 +4892,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="7" t="n">
         <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -4038,7 +4907,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4047,8 +4916,11 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="22" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -4074,7 +4946,7 @@
       <c r="F27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="22" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -4089,7 +4961,7 @@
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -4104,63 +4976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="20" min="1" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>처분이익계정명</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>처분손실계정명</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>유형자산처분이익</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>유형자산처분손실</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4281,7 +5097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4507,7 +5323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4715,7 +5531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4769,7 +5585,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C2" s="22" t="n">
+      <c r="C2" s="24" t="n">
         <v>1000000000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4794,7 +5610,7 @@
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" s="23" t="n">
+      <c r="C3" s="25" t="n">
         <v>1000000000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -4815,7 +5631,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="24" t="n">
         <v>500000000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4834,7 +5650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5260,7 +6076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5431,98 +6247,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>단기금융상품_MMF</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>단기금융상품_정기예금</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>미지급금(거래처)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>미지급금(사원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>미지급비용(급여)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>미지급비용(신용카드)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>미지급비용(이자)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>외상매입금</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>외상매출금</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>외주가공비(제조)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>계정과목 / 금액열 / 최소금액 / 실행여부 / 비고</t>
+          <t>계정과목 / 금액열(차변·대변·both) / 최소금액 / 실행여부 / 비고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정과목 (선택: 개수 / 금액열 열 추가 가능)</t>
+          <t>계정과목 (선택: 개수 / 금액열(차변·대변·both) 열 추가 가능)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>작업명 / 계정과목 / 거래처명 / 금액열 / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
+          <t>작업명 / 계정과목 / 거래처명 / 금액열(차변·대변·both) / 실행여부 / 관리단위(선택) / 비용구분(선택)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>계정과목 / 금액유형(차변·대변·차변대변모두) / 실행여부</t>
+          <t>계정과목 / 금액유형(차변·대변·both) / 실행여부</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -211,7 +211,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -282,6 +282,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2999,21 +3000,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="13" customWidth="1" style="20" min="1" max="2"/>
+    <col width="18" customWidth="1" style="20" min="1" max="2"/>
+    <col width="9" customWidth="1" style="20" min="2" max="2"/>
+    <col width="11" customWidth="1" style="20" min="3" max="3"/>
+    <col width="9" customWidth="1" style="20" min="4" max="4"/>
+    <col width="9" customWidth="1" style="20" min="5" max="5"/>
+    <col width="9" customWidth="1" style="20" min="6" max="6"/>
+    <col width="7" customWidth="1" style="20" min="7" max="7"/>
+    <col width="8" customWidth="1" style="20" min="8" max="8"/>
+    <col width="7" customWidth="1" style="20" min="9" max="9"/>
+    <col width="7" customWidth="1" style="20" min="10" max="10"/>
+    <col width="50" customWidth="1" style="20" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>샘플링비율</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>최소건수</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>최대건수</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>금액상위</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>최신</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>이상치</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>월별</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>랜덤</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>중점검토사항</t>
         </is>
       </c>
     </row>
@@ -3027,6 +3083,30 @@
         <is>
           <t>Y</t>
         </is>
+      </c>
+      <c r="C2" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G2" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J2" s="26" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3786,12 +3866,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>계정과목 / 실행여부</t>
+          <t>계정과목 / 실행여부 / 샘플링비율 / 최소건수 / 최대건수 / 금액상위 / 최신 / 이상치 / 월별 / 랜덤 / 중점검토사항(선택)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 비용 발생)</t>
+          <t>.env에 GEMINI_API_KEY 필요 (Gemini 실제 호출, 계정 1행당 1회 호출·비용 발생). 샘플크기 = 당기 거래건수 × 샘플링비율(최소~최대건수로 제한). 구성비(금액상위/최신/이상치/월별/랜덤)는 합계 100% 기준이며 합이 달라도 비율대로 자동 환산. 이상치 = 주말전기·금액이상치(IQR)·라운드금액(100만원 단위)·1회성거래처·적요미기재. 빈 칸은 기본값(5%, 30~150건, 30/20/10/30/10%). 중점검토사항에 적은 내용은 AI 분석 지시에 추가됨. 분석목록 26번 분석대상을 "전체"로 두면 전기 동기간 비교가 들어감(샘플은 당기에서만 추출)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>결과 시트 하나로 출력: 샘플링 / 계정요약 / 거래특징 / 경영자주장별 위험요소 / 감사인 제언 / 종합결론 / 확인필요전표 / 샘플내역 / 가명대조. AI에는 거래처·적요 속 실명은 가명, 직함 앞 사람이름·계좌번호는 마스킹해서 전송</t>
         </is>
       </c>
     </row>
@@ -4930,7 +5015,7 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립적으로 실행)</t>
+          <t>계정별 스마트샘플(비율·구성 지정) + 통계를 Gemini로 분석 — 계정요약/거래특징/경영자주장별 위험/감사인 제언</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
@@ -4940,7 +5025,7 @@
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="F27" s="18" t="n"/>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -16,17 +16,18 @@
     <sheet name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="17_거래처분석" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="21_총계정원장" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="22_은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="23_계정별 상세거래내역" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="24_리스완전성" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="25_손익월별분析" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="26_AI계정별분석_실행" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="27_감가상각_평가손익분석" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="유형자산_처분손익" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="25_손익월별분析" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -35,8 +36,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -211,7 +213,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -283,6 +285,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -826,6 +830,490 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="20" min="1" max="1"/>
+    <col width="9" customWidth="1" style="20" min="2" max="2"/>
+    <col width="12" customWidth="1" style="20" min="3" max="3"/>
+    <col width="12" customWidth="1" style="20" min="4" max="4"/>
+    <col width="11" customWidth="1" style="20" min="5" max="5"/>
+    <col width="9" customWidth="1" style="20" min="6" max="6"/>
+    <col width="9" customWidth="1" style="20" min="7" max="7"/>
+    <col width="10" customWidth="1" style="20" min="8" max="8"/>
+    <col width="9" customWidth="1" style="20" min="9" max="9"/>
+    <col width="15" customWidth="1" style="20" min="10" max="10"/>
+    <col width="13" customWidth="1" style="20" min="11" max="11"/>
+    <col width="11" customWidth="1" style="20" min="12" max="12"/>
+    <col width="15" customWidth="1" style="20" min="13" max="13"/>
+    <col width="40" customWidth="1" style="20" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>종료일</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>샘플링방법</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>금액타입</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>샘플크기</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>통계표사용</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>신뢰수준</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>허용왜곡표시</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>예상왜곡표시</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
+          <t>이상거래포함</t>
+        </is>
+      </c>
+      <c r="M1" s="18" t="inlineStr">
+        <is>
+          <t>개별유의금액</t>
+        </is>
+      </c>
+      <c r="N1" s="18" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="n"/>
+      <c r="D2" s="27" t="n"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I2" s="26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J2" s="28" t="n"/>
+      <c r="K2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M2" s="28" t="n"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>예시) 매출 실재성 — 차변 MUS 30건</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="n"/>
+      <c r="D3" s="27" t="n"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>체계적</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I3" s="26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J3" s="28" t="n"/>
+      <c r="K3" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M3" s="28" t="n"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>예시) 출금 증빙 — 대변 체계적 40건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J4" s="28" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="K4" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M4" s="28" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>예시) 통계표로 크기 계산 + 1천만원 이상 전수</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+    </row>
+    <row r="8">
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="27" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="27" t="n"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="27" t="n"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="27" t="n"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="n"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="n"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="27" t="n"/>
+      <c r="D40" s="27" t="n"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="27" t="n"/>
+    </row>
+    <row r="43">
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="27" t="n"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="27" t="n"/>
+      <c r="D44" s="27" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="27" t="n"/>
+      <c r="D45" s="27" t="n"/>
+    </row>
+    <row r="46">
+      <c r="C46" s="27" t="n"/>
+      <c r="D46" s="27" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="27" t="n"/>
+      <c r="D47" s="27" t="n"/>
+    </row>
+    <row r="48">
+      <c r="C48" s="27" t="n"/>
+      <c r="D48" s="27" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="27" t="n"/>
+      <c r="D49" s="27" t="n"/>
+    </row>
+    <row r="50">
+      <c r="C50" s="27" t="n"/>
+      <c r="D50" s="27" t="n"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="27" t="n"/>
+      <c r="D51" s="27" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="27" t="n"/>
+      <c r="D52" s="27" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="27" t="n"/>
+      <c r="D55" s="27" t="n"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="27" t="n"/>
+      <c r="D56" s="27" t="n"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="27" t="n"/>
+      <c r="D57" s="27" t="n"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="27" t="n"/>
+      <c r="D58" s="27" t="n"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="27" t="n"/>
+      <c r="D59" s="27" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"MUS,체계적,무작위,금액상위"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"차변,대변,both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B200 H2:H200 L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1011,7 +1499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1256,7 +1744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1945,7 +2433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2032,7 +2520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2730,7 +3218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2808,7 +3296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
@@ -2994,7 +3482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3114,164 +3602,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="30" customWidth="1" style="20" min="1" max="1"/>
-    <col width="10" customWidth="1" style="20" min="2" max="2"/>
-    <col width="12" customWidth="1" style="20" min="3" max="3"/>
-    <col width="10" customWidth="1" style="20" min="4" max="4"/>
-    <col width="55" customWidth="1" style="20" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>그룹기준열</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>외화환산손익</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>당기손익-공정가치측정금융자산평가손익</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>대손상각비</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>파생상품평가손익</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3636,17 +3966,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI계정별분석 (시트 미생성)</t>
+          <t>감사샘플링</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>계정과목 / 실행여부</t>
+          <t>계정과목 / 실행여부 / 시작일·종료일(선택) / 샘플링방법(MUS·체계적·무작위·금액상위) / 금액타입(차변·대변·both) / 샘플크기 / 통계표사용(Y/N) / 신뢰수준 / 허용왜곡표시 / 예상왜곡표시 / 이상거래포함(Y/N) / 개별유의금액(선택)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>쓰려면 시트명을 정확히 'AI계정별분석'으로 새로 만들고 계정과목 입력. Gemini 호출 없이 월별추이·샘플만 추출(26번과 형식은 같으나 AI 분석은 안 함)</t>
+          <t>계정 1줄 = 샘플링 1건, 샘플은 해당 계정의 전표 줄 단위(같은 전표의 상대계정 줄은 뽑지 않고 상대계정 열에 참고 표시). MUS=금액 누적 기준 구간마다 1건(구간보다 큰 줄은 반드시 선택) / 체계적=건수 기준 일정 간격 / 무작위 / 금액상위. 통계표사용=Y면 샘플크기 = 모집단금액×신뢰계수÷(허용왜곡표시−예상왜곡표시×확장계수) (95%: 3.0·1.6, 90%: 2.31·1.5). 이상거래포함=Y면 Z-score 3 이상·최대값을 샘플크기 안에서 우선 포함. 개별유의금액 이상은 샘플크기와 별도로 전수 포함. 시드 고정(42)이라 다시 돌려도 같은 샘플</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>결과: 샘플링조건(모집단·원장대사·크기근거·커버리지) + 계정별 샘플 시트(증빙종류·증빙확인·승인확인·예외사항·확인자 빈칸). AI로 보내지 않으므로 거래처·적요 실명 출력</t>
         </is>
       </c>
     </row>
@@ -3992,6 +4327,164 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="30" customWidth="1" style="20" min="1" max="1"/>
+    <col width="10" customWidth="1" style="20" min="2" max="2"/>
+    <col width="12" customWidth="1" style="20" min="3" max="3"/>
+    <col width="10" customWidth="1" style="20" min="4" max="4"/>
+    <col width="55" customWidth="1" style="20" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>외화환산손익</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>당기손익-공정가치측정금융자산평가손익</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>대손상각비</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>파생상품평가손익</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4295,7 +4788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4732,12 +5225,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI 계정별 분석</t>
+          <t>감사샘플링</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
+          <t>계정별 감사증빙 샘플 추출 (MUS/체계적/무작위/금액상위, 전표 줄 단위) → 15_감사샘플링 시트 참조</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -40,7 +40,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -115,8 +115,20 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
+    </font>
+    <font>
+      <color rgb="00404040"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -156,6 +168,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
   </fills>
@@ -213,7 +230,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -287,6 +304,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1180,94 +1200,209 @@
       <c r="D30" s="27" t="n"/>
     </row>
     <row r="31">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>■ 15번 감사샘플링 작성 안내 (이 안내 행들은 실행여부가 비어 있어 분석에 읽히지 않음 — 지우지 말고 위쪽 행에 계정 입력)</t>
+        </is>
+      </c>
       <c r="C31" s="27" t="n"/>
       <c r="D31" s="27" t="n"/>
     </row>
     <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>[기본 항목]</t>
+        </is>
+      </c>
       <c r="C32" s="27" t="n"/>
       <c r="D32" s="27" t="n"/>
     </row>
     <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>· 실행여부: Y(또는 O)인 행만 실행.  · 시작일/종료일: 비우면 분개장 전체 기간.</t>
+        </is>
+      </c>
       <c r="C33" s="27" t="n"/>
       <c r="D33" s="27" t="n"/>
     </row>
     <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>· 샘플링방법: MUS / 체계적 / 무작위 / 금액상위 (빈칸 = MUS).</t>
+        </is>
+      </c>
       <c r="C34" s="27" t="n"/>
       <c r="D34" s="27" t="n"/>
     </row>
     <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>· 금액타입: 차변 / 대변 / both (빈칸·그 외 값 = both). 결과시트명은 계정명_차 / _대 / _양.</t>
+        </is>
+      </c>
       <c r="C35" s="27" t="n"/>
       <c r="D35" s="27" t="n"/>
     </row>
     <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>[샘플크기 — 통계표사용에 따라 결정]</t>
+        </is>
+      </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="27" t="n"/>
     </row>
     <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>· 통계표사용 = N(또는 빈칸): 샘플크기 칸의 입력값대로 추출 (빈칸 = 30건). 신뢰수준·허용/예상왜곡표시는 무시됨.</t>
+        </is>
+      </c>
       <c r="C37" s="27" t="n"/>
       <c r="D37" s="27" t="n"/>
     </row>
     <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>· 통계표사용 = Y: 샘플크기 = 모집단금액 × 신뢰계수 ÷ (허용왜곡표시 − 예상왜곡표시 × 확장계수) 로 자동 계산, 샘플크기 칸 입력값은 무시됨.</t>
+        </is>
+      </c>
       <c r="C38" s="27" t="n"/>
       <c r="D38" s="27" t="n"/>
     </row>
     <row r="39">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 신뢰계수/확장계수: 90% = 2.31/1.5, 95% = 3.00/1.6, 99% = 4.61/1.9 (모집단금액은 개별유의금액 전수분을 뺀 금액).</t>
+        </is>
+      </c>
       <c r="C39" s="27" t="n"/>
       <c r="D39" s="27" t="n"/>
     </row>
     <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>· 신뢰수준: 0.95 또는 95 둘 다 가능 (빈칸 = 0.95). 90/95/99% 중 가까운 값 적용.</t>
+        </is>
+      </c>
       <c r="C40" s="27" t="n"/>
       <c r="D40" s="27" t="n"/>
     </row>
     <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>· 허용왜곡표시: 통계표사용 = Y이면 필수(예: 수행중요성). 비우면 해당 계정은 샘플 미추출 → 샘플링조건 시트 결과시트 "미추출" + 비고에 사유 표시.</t>
+        </is>
+      </c>
       <c r="C41" s="27" t="n"/>
       <c r="D41" s="27" t="n"/>
     </row>
     <row r="42">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>· 예상왜곡표시: 비워도 됨(빈칸 = 0). 0이면 샘플크기가 가장 작게 나오고, 전기 왜곡표시 등 오류 위험이 있으면 금액을 넣어 보수적으로(샘플 증가).</t>
+        </is>
+      </c>
       <c r="C42" s="27" t="n"/>
       <c r="D42" s="27" t="n"/>
     </row>
     <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 예상왜곡표시 × 확장계수 ≥ 허용왜곡표시 이면 계산 불가 → 해당 계정 건너뛰고 비고에 사유 표시.</t>
+        </is>
+      </c>
       <c r="C43" s="27" t="n"/>
       <c r="D43" s="27" t="n"/>
     </row>
     <row r="44">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>[금액 입력 형식 — 허용왜곡표시·예상왜곡표시·개별유의금액]</t>
+        </is>
+      </c>
       <c r="C44" s="27" t="n"/>
       <c r="D44" s="27" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>· 원 단위 숫자로 입력: 500000000 또는 500,000,000 (엑셀 숫자 셀 OK).</t>
+        </is>
+      </c>
       <c r="C45" s="27" t="n"/>
       <c r="D45" s="27" t="n"/>
     </row>
     <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>· "5억", "500,000,000원"처럼 글자가 섞이면 빈칸으로 처리됨. "5%", 0.05 같은 비율 입력 금지(5원·0.05원으로 읽힘).</t>
+        </is>
+      </c>
       <c r="C46" s="27" t="n"/>
       <c r="D46" s="27" t="n"/>
     </row>
     <row r="47">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>[추가 옵션]</t>
+        </is>
+      </c>
       <c r="C47" s="27" t="n"/>
       <c r="D47" s="27" t="n"/>
     </row>
     <row r="48">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t>· 개별유의금액: 이 금액 이상인 줄은 전수 추출(샘플크기와 별도로 추가). 빈칸 = 전수 없음.</t>
+        </is>
+      </c>
       <c r="C48" s="27" t="n"/>
       <c r="D48" s="27" t="n"/>
     </row>
     <row r="49">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t>· 이상거래포함 = Y: 최대값 + Z-score 3 이상 거래를 샘플크기의 20%까지 먼저 포함(샘플크기 안에 포함됨).</t>
+        </is>
+      </c>
       <c r="C49" s="27" t="n"/>
       <c r="D49" s="27" t="n"/>
     </row>
     <row r="50">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>[결과 확인]</t>
+        </is>
+      </c>
       <c r="C50" s="27" t="n"/>
       <c r="D50" s="27" t="n"/>
     </row>
     <row r="51">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>· 샘플링조건 시트: 계정별 모집단·원장 대사·샘플크기 근거·추출조건 요약. 샘플 시트가 안 나오면 이 시트의 결과시트·비고 열부터 확인.</t>
+        </is>
+      </c>
       <c r="C51" s="27" t="n"/>
       <c r="D51" s="27" t="n"/>
     </row>
     <row r="52">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t>· 샘플 단위는 해당 계정의 전표 "줄". 같은 전표의 상대계정 줄은 뽑지 않고 상대계정 열에 참고로만 표시.</t>
+        </is>
+      </c>
       <c r="C52" s="27" t="n"/>
       <c r="D52" s="27" t="n"/>
     </row>
     <row r="53">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t>· 시드 42 고정 → 같은 조건으로 재실행하면 같은 샘플(조서 재현성). 증빙종류~확인자 열은 감사인이 직접 기재.</t>
+        </is>
+      </c>
       <c r="C53" s="27" t="n"/>
       <c r="D53" s="27" t="n"/>
     </row>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="02_거래처 전기_당기 비교" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="03_벤포드 분석" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="08_상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="10_라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="25_손익월별분析" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석목록" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_거래처 전기_당기 비교" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_벤포드 분석" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_특수관계자 분석" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_감사샘플링" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_거래처분석" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_계정별 상세거래내역" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_리스완전성" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_손익월별분析" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_AI계정별분석_실행" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_감가상각_평가손익분석" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="감가상각_유형자산롤포워드" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유형자산_처분손익" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -384,6 +384,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>audit-automation</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>원장 적요에 포함된 문구(부분일치), 콤마(,)로 여러 개 지정 가능(OR). 기재하면 계정과목·거래처명·금액열 조건에 더해 적요 조건까지 만족하는 거래만 추출. 공란이면 적요 조건 없이 기존처럼 추출. 거래처명을 비우고 적요만 적으면 적요 기준으로 추출(거래처별 시트는 적요 문구별로 생성)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1453,19 +1468,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="18" customWidth="1" style="20" min="1" max="1"/>
     <col width="25" customWidth="1" style="20" min="2" max="2"/>
     <col width="35" customWidth="1" style="20" min="3" max="3"/>
-    <col width="10" customWidth="1" style="20" min="4" max="5"/>
+    <col width="25" customWidth="1" style="20" min="4" max="4"/>
+    <col width="10" customWidth="1" style="20" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="20">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명·적요는 콤마로 여러 개 가능 / 적요 기재 시 적요 조건도 추가(공란=조건 없음) / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
@@ -1487,10 +1503,15 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
+          <t>적요</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
           <t>금액열</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
@@ -1504,12 +1525,13 @@
       </c>
       <c r="B3" s="15" t="n"/>
       <c r="C3" s="15" t="n"/>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1523,12 +1545,13 @@
       </c>
       <c r="B4" s="15" t="n"/>
       <c r="C4" s="15" t="n"/>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1542,12 +1565,13 @@
       </c>
       <c r="B5" s="15" t="n"/>
       <c r="C5" s="15" t="n"/>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1561,12 +1585,13 @@
       </c>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="15" t="n"/>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1580,12 +1605,13 @@
       </c>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="15" t="n"/>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1595,42 +1621,48 @@
       <c r="A8" s="15" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="15" t="n"/>
-      <c r="D8" s="16" t="n"/>
+      <c r="D8" s="15" t="n"/>
       <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="20">
       <c r="A9" s="15" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="15" t="n"/>
-      <c r="D9" s="16" t="n"/>
+      <c r="D9" s="15" t="n"/>
       <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="20">
       <c r="A10" s="15" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="15" t="n"/>
-      <c r="D10" s="16" t="n"/>
+      <c r="D10" s="15" t="n"/>
       <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="20">
       <c r="A11" s="15" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="15" t="n"/>
-      <c r="D11" s="16" t="n"/>
+      <c r="D11" s="15" t="n"/>
       <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="20">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="15" t="n"/>
-      <c r="D12" s="16" t="n"/>
+      <c r="D12" s="15" t="n"/>
       <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
